--- a/sorento_crm_frontend/e2e/fixtures/debtor-listing.xlsx
+++ b/sorento_crm_frontend/e2e/fixtures/debtor-listing.xlsx
@@ -571,7 +571,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>016-225 8620</t>
+          <t>016-000 0505</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -598,7 +598,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>011-2233 4455</t>
+          <t>011-0000 0802</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
